--- a/12629229.xlsx
+++ b/12629229.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\cap776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420D4503-6874-41BD-A3C9-C2C2D83DCD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99C2F6F-F676-45FD-ACDA-DA6CBFC612D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,12 +388,12 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -877,70 +877,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12629229</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1174,7 +1174,7 @@
       <c r="A10" s="13">
         <v>46227</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="18">
         <v>440</v>
       </c>
       <c r="C10" s="9">
@@ -1266,7 +1266,7 @@
       <c r="A12" s="13">
         <v>46229</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="18">
         <v>450</v>
       </c>
       <c r="C12" s="9">
@@ -1358,7 +1358,7 @@
       <c r="A14" s="13">
         <v>46231</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="18">
         <v>460</v>
       </c>
       <c r="C14" s="9">
@@ -1450,7 +1450,7 @@
       <c r="A16" s="13">
         <v>46233</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="18">
         <v>470</v>
       </c>
       <c r="C16" s="9">
@@ -1542,7 +1542,7 @@
       <c r="A18" s="13">
         <v>46235</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="18">
         <v>440</v>
       </c>
       <c r="C18" s="9">
@@ -1634,7 +1634,7 @@
       <c r="A20" s="13">
         <v>46237</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="18">
         <v>450</v>
       </c>
       <c r="C20" s="9">
@@ -1772,14 +1772,14 @@
       <c r="A23" s="13">
         <v>46240</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="18">
         <v>470</v>
       </c>
       <c r="C23" s="9">
         <v>45</v>
       </c>
       <c r="D23" s="9">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E23" s="9">
         <v>30</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="2"/>
-        <v>790</v>
+        <v>740</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="3"/>
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>

--- a/12629229.xlsx
+++ b/12629229.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\cap776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AF29DA-A2ED-4DAF-AE42-C7E389838EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D675E-AD54-486D-8C7B-8E0A716F02AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="6" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="B6" s="10">
         <v>425</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="7" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B7" s="14">
         <v>500</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="8" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="B8" s="10">
         <v>480</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="9" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="B9" s="14">
         <v>420</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="10" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="B10" s="17">
         <v>440</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="11" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="B11" s="14">
         <v>445</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="12" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="B12" s="17">
         <v>450</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="13" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="B13" s="14">
         <v>455</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="14" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="B14" s="17">
         <v>460</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="15" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="B15" s="14">
         <v>465</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="16" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="B16" s="17">
         <v>470</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="17" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B17" s="14">
         <v>475</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="18" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="17">
         <v>440</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="19" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
-        <v>46236</v>
+        <v>46267</v>
       </c>
       <c r="B19" s="14">
         <v>445</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="20" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="B20" s="17">
         <v>450</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="21" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="B21" s="14">
         <v>455</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="22" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="B22" s="14">
         <v>465</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="23" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
-        <v>46240</v>
+        <v>46271</v>
       </c>
       <c r="B23" s="17">
         <v>470</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="24" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="B24" s="14">
         <v>500</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="25" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="B25" s="14">
         <v>480</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="26" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
-        <v>46243</v>
+        <v>46274</v>
       </c>
       <c r="B26" s="14">
         <v>430</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="27" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
-        <v>46244</v>
+        <v>46275</v>
       </c>
       <c r="B27" s="14">
         <v>500</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="28" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
-        <v>46245</v>
+        <v>46276</v>
       </c>
       <c r="B28" s="14">
         <v>480</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="29" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
-        <v>46246</v>
+        <v>46277</v>
       </c>
       <c r="B29" s="14">
         <v>400</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="30" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
-        <v>46247</v>
+        <v>46278</v>
       </c>
       <c r="B30" s="14">
         <v>500</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="31" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
-        <v>46248</v>
+        <v>46279</v>
       </c>
       <c r="B31" s="14">
         <v>480</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="32" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="B32" s="14">
         <v>430</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="33" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
-        <v>46250</v>
+        <v>46281</v>
       </c>
       <c r="B33" s="17">
         <v>440</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="34" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
-        <v>46251</v>
+        <v>46282</v>
       </c>
       <c r="B34" s="14">
         <v>445</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="35" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
-        <v>46252</v>
+        <v>46283</v>
       </c>
       <c r="B35" s="17">
         <v>450</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="36" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
-        <v>46253</v>
+        <v>46284</v>
       </c>
       <c r="B36" s="14">
         <v>480</v>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="37" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
-        <v>46254</v>
+        <v>46285</v>
       </c>
       <c r="B37" s="14">
         <v>500</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="38" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
-        <v>46255</v>
+        <v>46286</v>
       </c>
       <c r="B38" s="14">
         <v>450</v>

--- a/12629229.xlsx
+++ b/12629229.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\cap776\cap776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\minor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D675E-AD54-486D-8C7B-8E0A716F02AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2A78E8-09AB-4C2D-9044-A3E7C506DCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>AUGUST</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1019,7 @@
     </row>
     <row r="6" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>46254</v>
+        <v>46247</v>
       </c>
       <c r="B6" s="10">
         <v>425</v>
@@ -1040,11 +1043,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="11">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f>IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>910</v>
       </c>
       <c r="J6" s="11">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f>IF(I6="","",1440-I6)</f>
         <v>530</v>
       </c>
       <c r="K6" s="12" t="s">
@@ -1062,7 +1065,7 @@
     </row>
     <row r="7" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="B7" s="14">
         <v>500</v>
@@ -1086,11 +1089,11 @@
         <v>30</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1045</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I7="","",1440-I7)</f>
         <v>395</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1108,7 +1111,7 @@
     </row>
     <row r="8" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="10">
         <v>480</v>
@@ -1132,11 +1135,11 @@
         <v>30</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>800</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I8="","",1440-I8)</f>
         <v>640</v>
       </c>
       <c r="K8" s="12" t="s">
@@ -1154,7 +1157,7 @@
     </row>
     <row r="9" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="B9" s="14">
         <v>420</v>
@@ -1178,11 +1181,11 @@
         <v>50</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
         <v>795</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I9="","",1440-I9)</f>
         <v>645</v>
       </c>
       <c r="K9" s="16" t="s">
@@ -1200,7 +1203,7 @@
     </row>
     <row r="10" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B10" s="17">
         <v>440</v>
@@ -1224,11 +1227,11 @@
         <v>60</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
         <v>920</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I10="","",1440-I10)</f>
         <v>520</v>
       </c>
       <c r="K10" s="12" t="s">
@@ -1246,7 +1249,7 @@
     </row>
     <row r="11" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="14">
         <v>445</v>
@@ -1270,11 +1273,11 @@
         <v>45</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>980</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I11="","",1440-I11)</f>
         <v>460</v>
       </c>
       <c r="K11" s="16" t="s">
@@ -1292,7 +1295,7 @@
     </row>
     <row r="12" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="B12" s="17">
         <v>450</v>
@@ -1316,11 +1319,11 @@
         <v>60</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
         <v>1035</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I12="","",1440-I12)</f>
         <v>405</v>
       </c>
       <c r="K12" s="12" t="s">
@@ -1338,7 +1341,7 @@
     </row>
     <row r="13" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B13" s="14">
         <v>455</v>
@@ -1362,11 +1365,11 @@
         <v>30</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
         <v>895</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I13="","",1440-I13)</f>
         <v>545</v>
       </c>
       <c r="K13" s="16" t="s">
@@ -1384,7 +1387,7 @@
     </row>
     <row r="14" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="B14" s="17">
         <v>460</v>
@@ -1408,11 +1411,11 @@
         <v>25</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
         <v>895</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I14="","",1440-I14)</f>
         <v>545</v>
       </c>
       <c r="K14" s="12" t="s">
@@ -1430,7 +1433,7 @@
     </row>
     <row r="15" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="14">
         <v>465</v>
@@ -1454,11 +1457,11 @@
         <v>40</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
         <v>835</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I15="","",1440-I15)</f>
         <v>605</v>
       </c>
       <c r="K15" s="16" t="s">
@@ -1476,7 +1479,7 @@
     </row>
     <row r="16" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="17">
         <v>470</v>
@@ -1500,11 +1503,11 @@
         <v>45</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
         <v>790</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I16="","",1440-I16)</f>
         <v>650</v>
       </c>
       <c r="K16" s="12" t="s">
@@ -1522,7 +1525,7 @@
     </row>
     <row r="17" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B17" s="14">
         <v>475</v>
@@ -1546,11 +1549,11 @@
         <v>30</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
         <v>860</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I17="","",1440-I17)</f>
         <v>580</v>
       </c>
       <c r="K17" s="16" t="s">
@@ -1568,7 +1571,7 @@
     </row>
     <row r="18" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="17">
         <v>440</v>
@@ -1592,11 +1595,11 @@
         <v>60</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
         <v>920</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I18="","",1440-I18)</f>
         <v>520</v>
       </c>
       <c r="K18" s="12" t="s">
@@ -1614,7 +1617,7 @@
     </row>
     <row r="19" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="14">
         <v>445</v>
@@ -1638,11 +1641,11 @@
         <v>45</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
         <v>980</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I19="","",1440-I19)</f>
         <v>460</v>
       </c>
       <c r="K19" s="16" t="s">
@@ -1660,7 +1663,7 @@
     </row>
     <row r="20" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="17">
         <v>450</v>
@@ -1684,11 +1687,11 @@
         <v>60</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
         <v>1035</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I20="","",1440-I20)</f>
         <v>405</v>
       </c>
       <c r="K20" s="12" t="s">
@@ -1706,7 +1709,7 @@
     </row>
     <row r="21" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="14">
         <v>455</v>
@@ -1730,11 +1733,11 @@
         <v>30</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
         <v>895</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I21="","",1440-I21)</f>
         <v>545</v>
       </c>
       <c r="K21" s="12" t="s">
@@ -1752,7 +1755,7 @@
     </row>
     <row r="22" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="B22" s="14">
         <v>465</v>
@@ -1776,11 +1779,11 @@
         <v>40</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" ref="I22:I23" si="2">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>835</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" ref="J22:J23" si="3">IF(I22="","",1440-I22)</f>
+        <f>IF(I22="","",1440-I22)</f>
         <v>605</v>
       </c>
       <c r="K22" s="16" t="s">
@@ -1798,7 +1801,7 @@
     </row>
     <row r="23" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="B23" s="17">
         <v>470</v>
@@ -1822,11 +1825,11 @@
         <v>45</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v>890</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="3"/>
+        <f>IF(I23="","",1440-I23)</f>
         <v>550</v>
       </c>
       <c r="K23" s="12" t="s">
@@ -1844,7 +1847,7 @@
     </row>
     <row r="24" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B24" s="14">
         <v>500</v>
@@ -1868,11 +1871,11 @@
         <v>45</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
         <v>1315</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I24="","",1440-I24)</f>
         <v>125</v>
       </c>
       <c r="K24" s="16" t="s">
@@ -1890,7 +1893,7 @@
     </row>
     <row r="25" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="B25" s="14">
         <v>480</v>
@@ -1914,11 +1917,11 @@
         <v>40</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
         <v>1195</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I25="","",1440-I25)</f>
         <v>245</v>
       </c>
       <c r="K25" s="16" t="s">
@@ -1936,7 +1939,7 @@
     </row>
     <row r="26" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B26" s="14">
         <v>430</v>
@@ -1960,11 +1963,11 @@
         <v>45</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
         <v>1325</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I26="","",1440-I26)</f>
         <v>115</v>
       </c>
       <c r="K26" s="16" t="s">
@@ -1982,7 +1985,7 @@
     </row>
     <row r="27" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B27" s="14">
         <v>500</v>
@@ -2006,11 +2009,11 @@
         <v>200</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
         <v>1185</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I27="","",1440-I27)</f>
         <v>255</v>
       </c>
       <c r="K27" s="16" t="s">
@@ -2028,7 +2031,7 @@
     </row>
     <row r="28" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="B28" s="14">
         <v>480</v>
@@ -2052,11 +2055,11 @@
         <v>40</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
         <v>1440</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I28="","",1440-I28)</f>
         <v>0</v>
       </c>
       <c r="K28" s="16" t="s">
@@ -2074,7 +2077,7 @@
     </row>
     <row r="29" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="B29" s="14">
         <v>400</v>
@@ -2098,11 +2101,11 @@
         <v>60</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
         <v>1380</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I29="","",1440-I29)</f>
         <v>60</v>
       </c>
       <c r="K29" s="16" t="s">
@@ -2120,7 +2123,7 @@
     </row>
     <row r="30" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="B30" s="14">
         <v>500</v>
@@ -2144,11 +2147,11 @@
         <v>45</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:I35" si="4">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
         <v>1015</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" ref="J30:J35" si="5">IF(I30="","",1440-I30)</f>
+        <f>IF(I30="","",1440-I30)</f>
         <v>425</v>
       </c>
       <c r="K30" s="16" t="s">
@@ -2166,7 +2169,7 @@
     </row>
     <row r="31" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B31" s="14">
         <v>480</v>
@@ -2190,11 +2193,11 @@
         <v>40</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
         <v>1295</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="5"/>
+        <f>IF(I31="","",1440-I31)</f>
         <v>145</v>
       </c>
       <c r="K31" s="16" t="s">
@@ -2212,7 +2215,7 @@
     </row>
     <row r="32" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B32" s="14">
         <v>430</v>
@@ -2236,11 +2239,11 @@
         <v>45</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
         <v>1125</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="5"/>
+        <f>IF(I32="","",1440-I32)</f>
         <v>315</v>
       </c>
       <c r="K32" s="16" t="s">
@@ -2258,7 +2261,7 @@
     </row>
     <row r="33" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="B33" s="17">
         <v>440</v>
@@ -2282,11 +2285,11 @@
         <v>60</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
         <v>1170</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="5"/>
+        <f>IF(I33="","",1440-I33)</f>
         <v>270</v>
       </c>
       <c r="K33" s="12" t="s">
@@ -2304,7 +2307,7 @@
     </row>
     <row r="34" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B34" s="14">
         <v>445</v>
@@ -2328,11 +2331,11 @@
         <v>45</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
         <v>1030</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="5"/>
+        <f>IF(I34="","",1440-I34)</f>
         <v>410</v>
       </c>
       <c r="K34" s="16" t="s">
@@ -2350,7 +2353,7 @@
     </row>
     <row r="35" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="B35" s="17">
         <v>450</v>
@@ -2374,11 +2377,11 @@
         <v>60</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
         <v>1035</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="5"/>
+        <f>IF(I35="","",1440-I35)</f>
         <v>405</v>
       </c>
       <c r="K35" s="12" t="s">
@@ -2396,7 +2399,7 @@
     </row>
     <row r="36" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="B36" s="14">
         <v>480</v>
@@ -2420,11 +2423,11 @@
         <v>40</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
         <v>1110</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I36="","",1440-I36)</f>
         <v>330</v>
       </c>
       <c r="K36" s="12" t="s">
@@ -2442,7 +2445,7 @@
     </row>
     <row r="37" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="B37" s="14">
         <v>500</v>
@@ -2466,11 +2469,11 @@
         <v>60</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
         <v>800</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I37="","",1440-I37)</f>
         <v>640</v>
       </c>
       <c r="K37" s="12" t="s">
@@ -2488,7 +2491,7 @@
     </row>
     <row r="38" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B38" s="14">
         <v>450</v>
@@ -2512,11 +2515,11 @@
         <v>45</v>
       </c>
       <c r="I38" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
         <v>1095</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I38="","",1440-I38)</f>
         <v>345</v>
       </c>
       <c r="K38" s="12" t="s">
@@ -2533,161 +2536,329 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="18"/>
+      <c r="A39" s="9">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="14">
+        <v>500</v>
+      </c>
+      <c r="C39" s="14">
+        <v>90</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>200</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>45</v>
+      </c>
+      <c r="I39" s="15">
+        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
+        <v>1315</v>
+      </c>
+      <c r="J39" s="15">
+        <f>IF(I39="","",1440-I39)</f>
+        <v>125</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="18"/>
+      <c r="A40" s="9">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>95</v>
+      </c>
+      <c r="D40" s="14">
+        <v>200</v>
+      </c>
+      <c r="E40" s="14">
+        <v>180</v>
+      </c>
+      <c r="F40" s="14">
+        <v>200</v>
+      </c>
+      <c r="G40" s="14">
+        <v>8</v>
+      </c>
+      <c r="H40" s="14">
+        <v>40</v>
+      </c>
+      <c r="I40" s="15">
+        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <v>1195</v>
+      </c>
+      <c r="J40" s="15">
+        <f>IF(I40="","",1440-I40)</f>
+        <v>245</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="41" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="18"/>
+      <c r="A41" s="9">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="14">
+        <v>430</v>
+      </c>
+      <c r="C41" s="14">
+        <v>120</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>150</v>
+      </c>
+      <c r="F41" s="14">
+        <v>400</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>45</v>
+      </c>
+      <c r="I41" s="15">
+        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <v>1325</v>
+      </c>
+      <c r="J41" s="15">
+        <f>IF(I41="","",1440-I41)</f>
+        <v>115</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="18"/>
+      <c r="A42" s="9">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="14">
+        <v>500</v>
+      </c>
+      <c r="C42" s="14">
+        <v>115</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>100</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
+        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <v>1185</v>
+      </c>
+      <c r="J42" s="15">
+        <f>IF(I42="","",1440-I42)</f>
+        <v>255</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="18"/>
+      <c r="A43" s="9">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>120</v>
+      </c>
+      <c r="D43" s="14">
+        <v>500</v>
+      </c>
+      <c r="E43" s="14">
+        <v>200</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>40</v>
+      </c>
+      <c r="I43" s="15">
+        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <v>1340</v>
+      </c>
+      <c r="J43" s="15">
+        <f>IF(I43="","",1440-I43)</f>
+        <v>100</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="18"/>
+      <c r="A44" s="9">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>150</v>
+      </c>
+      <c r="E44" s="14">
+        <v>400</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>40</v>
+      </c>
+      <c r="I44" s="15">
+        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <v>1110</v>
+      </c>
+      <c r="J44" s="15">
+        <f>IF(I44="","",1440-I44)</f>
+        <v>330</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="18"/>
+      <c r="A45" s="9">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="14">
+        <v>500</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
+        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <v>1100</v>
+      </c>
+      <c r="J45" s="15">
+        <f>IF(I45="","",1440-I45)</f>
+        <v>340</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="46" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
+      <c r="A46" s="9"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2696,11 +2867,11 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I44:I69" si="0">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
         <v/>
       </c>
       <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J44:J69" si="1">IF(I46="","",1440-I46)</f>
         <v/>
       </c>
       <c r="K46" s="16"/>
@@ -2709,7 +2880,7 @@
       <c r="N46" s="18"/>
     </row>
     <row r="47" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
+      <c r="A47" s="9"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2731,7 +2902,7 @@
       <c r="N47" s="18"/>
     </row>
     <row r="48" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
+      <c r="A48" s="9"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2753,7 +2924,7 @@
       <c r="N48" s="18"/>
     </row>
     <row r="49" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
+      <c r="A49" s="9"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2775,7 +2946,7 @@
       <c r="N49" s="18"/>
     </row>
     <row r="50" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="19"/>
+      <c r="A50" s="9"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2797,7 +2968,7 @@
       <c r="N50" s="18"/>
     </row>
     <row r="51" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
+      <c r="A51" s="9"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2819,7 +2990,7 @@
       <c r="N51" s="18"/>
     </row>
     <row r="52" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="19"/>
+      <c r="A52" s="9"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2841,7 +3012,7 @@
       <c r="N52" s="18"/>
     </row>
     <row r="53" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
+      <c r="A53" s="9"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2863,7 +3034,7 @@
       <c r="N53" s="18"/>
     </row>
     <row r="54" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="19"/>
+      <c r="A54" s="9"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2885,7 +3056,7 @@
       <c r="N54" s="18"/>
     </row>
     <row r="55" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
+      <c r="A55" s="9"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2907,7 +3078,7 @@
       <c r="N55" s="18"/>
     </row>
     <row r="56" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="19"/>
+      <c r="A56" s="9"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2929,7 +3100,7 @@
       <c r="N56" s="18"/>
     </row>
     <row r="57" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
+      <c r="A57" s="9"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2951,7 +3122,7 @@
       <c r="N57" s="18"/>
     </row>
     <row r="58" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
+      <c r="A58" s="9"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2973,7 +3144,7 @@
       <c r="N58" s="18"/>
     </row>
     <row r="59" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
+      <c r="A59" s="9"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2995,7 +3166,7 @@
       <c r="N59" s="18"/>
     </row>
     <row r="60" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="19"/>
+      <c r="A60" s="9"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3017,7 +3188,7 @@
       <c r="N60" s="18"/>
     </row>
     <row r="61" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
+      <c r="A61" s="9"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3039,7 +3210,7 @@
       <c r="N61" s="18"/>
     </row>
     <row r="62" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="19"/>
+      <c r="A62" s="9"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3061,7 +3232,7 @@
       <c r="N62" s="18"/>
     </row>
     <row r="63" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
+      <c r="A63" s="9"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3083,7 +3254,7 @@
       <c r="N63" s="18"/>
     </row>
     <row r="64" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="19"/>
+      <c r="A64" s="9"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3105,7 +3276,7 @@
       <c r="N64" s="18"/>
     </row>
     <row r="65" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
+      <c r="A65" s="9"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3127,7 +3298,7 @@
       <c r="N65" s="18"/>
     </row>
     <row r="66" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="19"/>
+      <c r="A66" s="9"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3149,7 +3320,7 @@
       <c r="N66" s="18"/>
     </row>
     <row r="67" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="19"/>
+      <c r="A67" s="9"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3171,7 +3342,7 @@
       <c r="N67" s="18"/>
     </row>
     <row r="68" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="19"/>
+      <c r="A68" s="9"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3193,7 +3364,7 @@
       <c r="N68" s="18"/>
     </row>
     <row r="69" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="19"/>
+      <c r="A69" s="9"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3215,7 +3386,7 @@
       <c r="N69" s="18"/>
     </row>
     <row r="70" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="19"/>
+      <c r="A70" s="9"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3224,11 +3395,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3237,7 +3408,7 @@
       <c r="N70" s="18"/>
     </row>
     <row r="71" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="19"/>
+      <c r="A71" s="9"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3246,11 +3417,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3259,7 +3430,7 @@
       <c r="N71" s="18"/>
     </row>
     <row r="72" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="19"/>
+      <c r="A72" s="9"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3268,11 +3439,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3281,7 +3452,7 @@
       <c r="N72" s="18"/>
     </row>
     <row r="73" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="19"/>
+      <c r="A73" s="9"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3290,11 +3461,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3303,7 +3474,7 @@
       <c r="N73" s="18"/>
     </row>
     <row r="74" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="19"/>
+      <c r="A74" s="9"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3312,11 +3483,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3325,7 +3496,7 @@
       <c r="N74" s="18"/>
     </row>
     <row r="75" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
+      <c r="A75" s="9"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3334,11 +3505,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3347,7 +3518,7 @@
       <c r="N75" s="18"/>
     </row>
     <row r="76" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="19"/>
+      <c r="A76" s="9"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3356,11 +3527,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3369,7 +3540,7 @@
       <c r="N76" s="18"/>
     </row>
     <row r="77" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
+      <c r="A77" s="9"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3378,11 +3549,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3391,7 +3562,7 @@
       <c r="N77" s="18"/>
     </row>
     <row r="78" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="19"/>
+      <c r="A78" s="9"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3400,11 +3571,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3422,11 +3593,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3444,11 +3615,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3466,11 +3637,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3488,11 +3659,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3510,11 +3681,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3532,11 +3703,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3554,11 +3725,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3576,11 +3747,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3598,11 +3769,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3620,11 +3791,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3642,11 +3813,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3664,11 +3835,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3686,11 +3857,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3708,11 +3879,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3730,11 +3901,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3752,11 +3923,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3774,11 +3945,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3796,11 +3967,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3818,11 +3989,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3840,11 +4011,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3862,11 +4033,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3884,11 +4055,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3906,11 +4077,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3928,11 +4099,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3950,11 +4121,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3972,11 +4143,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3994,11 +4165,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4016,11 +4187,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4038,11 +4209,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4060,11 +4231,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4082,11 +4253,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4104,11 +4275,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4126,11 +4297,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4148,11 +4319,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4170,11 +4341,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4192,11 +4363,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4214,11 +4385,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4236,11 +4407,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4258,11 +4429,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4280,11 +4451,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4302,11 +4473,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4324,11 +4495,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4346,11 +4517,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4368,11 +4539,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4390,11 +4561,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4412,11 +4583,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4434,11 +4605,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4456,11 +4627,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4478,11 +4649,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4500,11 +4671,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4522,11 +4693,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4544,11 +4715,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4566,11 +4737,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4588,11 +4759,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4610,11 +4781,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4632,11 +4803,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4654,11 +4825,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4676,11 +4847,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4698,11 +4869,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4720,11 +4891,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4742,11 +4913,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4764,11 +4935,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4786,11 +4957,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4808,11 +4979,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4830,11 +5001,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4852,11 +5023,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4874,11 +5045,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4896,11 +5067,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4918,11 +5089,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4940,11 +5111,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4962,11 +5133,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4984,11 +5155,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5006,11 +5177,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5028,11 +5199,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5050,11 +5221,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5072,11 +5243,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5094,11 +5265,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5116,11 +5287,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5138,11 +5309,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5160,11 +5331,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5182,11 +5353,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5204,11 +5375,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5226,11 +5397,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5248,11 +5419,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5270,11 +5441,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5292,11 +5463,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5314,11 +5485,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5336,11 +5507,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5358,11 +5529,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5380,11 +5551,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5402,11 +5573,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5424,11 +5595,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5446,11 +5617,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5468,11 +5639,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5490,11 +5661,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5512,11 +5683,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5534,11 +5705,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5556,11 +5727,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5578,11 +5749,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5600,11 +5771,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5622,11 +5793,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5644,11 +5815,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5666,11 +5837,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5688,11 +5859,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5710,11 +5881,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5732,11 +5903,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5754,11 +5925,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5776,11 +5947,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5798,11 +5969,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5820,11 +5991,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5842,11 +6013,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5864,11 +6035,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5886,11 +6057,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5908,11 +6079,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5930,11 +6101,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5952,11 +6123,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5974,11 +6145,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5996,11 +6167,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6018,11 +6189,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6040,11 +6211,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6062,11 +6233,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6084,11 +6255,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6106,11 +6277,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6128,11 +6299,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6150,11 +6321,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6172,11 +6343,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6194,11 +6365,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6216,11 +6387,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6238,11 +6409,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6260,11 +6431,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6282,11 +6453,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6304,11 +6475,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6326,11 +6497,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6348,11 +6519,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6370,11 +6541,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6392,11 +6563,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6414,11 +6585,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6436,11 +6607,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6458,11 +6629,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6480,11 +6651,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6502,11 +6673,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6524,11 +6695,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6546,11 +6717,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6568,11 +6739,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6590,11 +6761,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6612,11 +6783,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6634,11 +6805,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6656,11 +6827,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6678,11 +6849,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6700,11 +6871,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6722,11 +6893,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6744,11 +6915,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6766,11 +6937,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6788,11 +6959,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6810,11 +6981,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6832,11 +7003,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6854,11 +7025,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6876,11 +7047,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6898,11 +7069,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6920,11 +7091,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6942,11 +7113,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6964,11 +7135,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6986,11 +7157,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7008,11 +7179,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7030,11 +7201,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7052,11 +7223,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7074,11 +7245,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7096,11 +7267,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7118,11 +7289,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7140,11 +7311,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7162,11 +7333,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7184,11 +7355,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7206,11 +7377,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7228,11 +7399,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7250,11 +7421,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7272,11 +7443,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7294,11 +7465,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7316,11 +7487,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7338,11 +7509,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7360,11 +7531,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7382,11 +7553,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7404,11 +7575,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7426,11 +7597,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7448,11 +7619,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7470,11 +7641,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7492,11 +7663,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7514,11 +7685,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7536,11 +7707,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7558,11 +7729,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7580,11 +7751,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7602,11 +7773,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7624,11 +7795,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7646,11 +7817,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7668,11 +7839,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7690,11 +7861,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7712,11 +7883,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7734,11 +7905,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7756,11 +7927,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7778,11 +7949,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7800,11 +7971,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7822,11 +7993,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7844,11 +8015,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7866,11 +8037,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7888,11 +8059,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7910,11 +8081,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7932,11 +8103,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7954,11 +8125,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7976,11 +8147,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7998,11 +8169,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8020,11 +8191,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8042,11 +8213,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8064,11 +8235,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8086,11 +8257,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8108,11 +8279,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8130,11 +8301,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8152,11 +8323,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8174,11 +8345,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8196,11 +8367,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8218,11 +8389,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8240,11 +8411,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8262,11 +8433,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8284,11 +8455,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8306,11 +8477,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8328,11 +8499,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8350,11 +8521,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8372,11 +8543,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8394,11 +8565,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8416,11 +8587,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8438,11 +8609,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8460,11 +8631,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8482,11 +8653,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8504,11 +8675,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8526,11 +8697,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8548,11 +8719,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8570,11 +8741,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8592,11 +8763,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8614,11 +8785,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8636,11 +8807,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8658,11 +8829,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8680,11 +8851,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8702,11 +8873,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8724,11 +8895,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8746,11 +8917,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8768,11 +8939,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8790,11 +8961,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8812,11 +8983,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8834,11 +9005,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8856,11 +9027,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8878,11 +9049,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8900,11 +9071,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8922,11 +9093,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8944,11 +9115,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8966,11 +9137,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8988,11 +9159,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9010,11 +9181,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9032,11 +9203,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9054,11 +9225,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9076,11 +9247,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9098,11 +9269,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9120,11 +9291,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9142,11 +9313,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9164,11 +9335,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9186,11 +9357,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9208,11 +9379,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9230,11 +9401,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9252,11 +9423,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9274,11 +9445,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9296,11 +9467,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9318,11 +9489,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9340,11 +9511,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9362,11 +9533,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9384,11 +9555,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9406,11 +9577,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9428,11 +9599,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9450,11 +9621,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9472,11 +9643,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9494,11 +9665,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9516,11 +9687,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9538,11 +9709,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9560,11 +9731,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9582,11 +9753,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9604,11 +9775,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9626,11 +9797,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9648,11 +9819,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9670,11 +9841,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9692,11 +9863,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9714,11 +9885,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9736,11 +9907,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9758,11 +9929,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9780,11 +9951,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9802,11 +9973,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9824,11 +9995,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9846,11 +10017,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9868,11 +10039,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9890,11 +10061,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9912,11 +10083,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9934,11 +10105,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9956,11 +10127,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9978,11 +10149,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10000,11 +10171,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10022,11 +10193,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10044,11 +10215,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10066,11 +10237,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10088,11 +10259,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10110,11 +10281,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10132,11 +10303,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10154,11 +10325,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10176,11 +10347,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10198,11 +10369,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10220,11 +10391,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10242,11 +10413,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10264,11 +10435,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10286,11 +10457,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10308,11 +10479,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10330,11 +10501,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10352,11 +10523,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10374,11 +10545,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10396,11 +10567,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10418,11 +10589,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10440,11 +10611,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10462,11 +10633,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10484,11 +10655,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10506,11 +10677,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
